--- a/results/job_matches_2026-05-18.xlsx
+++ b/results/job_matches_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Azure Fabric Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
+          <t>https://www.indeed.com/viewjob?jk=794bf3e65cff79af</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76fbdb48e9a34d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b7f11613741a49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Engineer Specialist</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Jenkins, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,77 +601,287 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c3d08d72035c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=990147cfb670b11e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
+          <t>https://www.indeed.com/viewjob?jk=c9219030cb1ff76f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Azure Fabric Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cyberlocke, LLC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>McKinney, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5da77bc70804a17c</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cloud Engineer Specialist</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technology Ventures</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97c3d08d72035c3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d4445654d17d84f</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Casey's</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ankeny, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Mid-Level Azure DevOps Engineer</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Cyberlocke, LLC</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>McKinney, TX, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D12" t="n">
         <v>11.1</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>RDS, Azure, Data Factory, Medallion Architecture, ETL, ELT, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Engineer and Developer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, PostgreSQL, ETL, dbt, Tableau, Airflow, Apache Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a627bc801113951</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-18.xlsx
+++ b/results/job_matches_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Observability Engineer (Prometheus / Grafana / Datadog)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LifeMD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb8735550d94e63</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba2ab0e8ae4be68</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LifeMD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Huntington Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794bf3e65cff79af</t>
+          <t>https://www.indeed.com/viewjob?jk=3f2e0fa3bcda75e7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Architect</t>
+          <t>Observability Engineer (Prometheus / Grafana / Datadog)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b7f11613741a49</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb8735550d94e63</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Senior Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990147cfb670b11e</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b7f11613741a49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Azure Fabric Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9219030cb1ff76f</t>
+          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Fabric Engineer</t>
+          <t>Data Analyst (70002877)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,69 +661,69 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd2e5a47e38462e2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Cloud Engineer Specialist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5da77bc70804a17c</t>
+          <t>https://www.indeed.com/viewjob?jk=97c3d08d72035c3d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Engineer Specialist</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,155 +731,120 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c3d08d72035c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Mid-Level Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, ETL, ELT, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4445654d17d84f</t>
+          <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Ledger Operations Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d65ad8442e8885d</t>
+          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mid-Level Azure DevOps Engineer</t>
+          <t>Data Engineer and Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, ETL, ELT, Power BI, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, PostgreSQL, ETL, dbt, Tableau, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Data Engineer and Developer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, PostgreSQL, ETL, dbt, Tableau, Airflow, Apache Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9a627bc801113951</t>
         </is>

--- a/results/job_matches_2026-05-18.xlsx
+++ b/results/job_matches_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Fabric Engineer</t>
+          <t>Data Analyst (70002877)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,69 +626,69 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Cloud Storage, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b1d946f299c08c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd2e5a47e38462e2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Analyst (70002877)</t>
+          <t>Cloud Engineer Specialist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd2e5a47e38462e2</t>
+          <t>https://www.indeed.com/viewjob?jk=97c3d08d72035c3d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Engineer Specialist</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,69 +696,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c3d08d72035c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Platform Engineer-US</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Certinia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mid-Level Azure DevOps Engineer</t>
+          <t>Senior Ledger Operations Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,24 +766,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, ETL, ELT, Power BI, CI/CD, Azure DevOps, Terraform</t>
+          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed58b32ec5793dff</t>
+          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Ledger Operations Engineer</t>
+          <t>Data Engineer and Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, PostgreSQL, ETL, dbt, Tableau, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -810,41 +810,6 @@
         </is>
       </c>
       <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Data Engineer and Developer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, PostgreSQL, ETL, dbt, Tableau, Airflow, Apache Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9a627bc801113951</t>
         </is>

--- a/results/job_matches_2026-05-18.xlsx
+++ b/results/job_matches_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,35 +643,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Engineer Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Alphanumeric Systems Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c3d08d72035c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=aafc1066893dd26c</t>
         </is>
       </c>
     </row>
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Platform Engineer-US</t>
+          <t>Front-end Programmer Developer - II or Senior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Certinia</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
+          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Ledger Operations Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RX USA LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Souderton, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,182 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Platform Engineer-US</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Certinia</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Ledger Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Data Engineer and Developer</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D13" t="n">
         <v>10.4</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, PostgreSQL, ETL, dbt, Tableau, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9a627bc801113951</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Security Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SUPPLIER.IO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62fecc0c2154e4b1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-18.xlsx
+++ b/results/job_matches_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data and Insight Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LifeMD</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,17 +486,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba2ab0e8ae4be68</t>
+          <t>https://www.indeed.com/viewjob?jk=bb46af131203645d</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Huntington Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f2e0fa3bcda75e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba2ab0e8ae4be68</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Observability Engineer (Prometheus / Grafana / Datadog)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LifeMD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Huntington Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb8735550d94e63</t>
+          <t>https://www.indeed.com/viewjob?jk=3f2e0fa3bcda75e7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Architect</t>
+          <t>Observability Engineer (Prometheus / Grafana / Datadog)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b7f11613741a49</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb8735550d94e63</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Analyst (70002877)</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Vanda Pharmaceuticals</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd2e5a47e38462e2</t>
+          <t>https://www.indeed.com/viewjob?jk=f51f479af9282287</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alphanumeric Systems Inc</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafc1066893dd26c</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b7f11613741a49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Front-end Programmer Developer - II or Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RX USA LLC</t>
+          <t>Alphanumeric Systems Inc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Souderton, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
+          <t>https://www.indeed.com/viewjob?jk=aafc1066893dd26c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Platform Engineer-US</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Certinia</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
+          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Ledger Operations Engineer</t>
+          <t>Front-end Programmer Developer - II or Senior</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
+          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer and Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RX USA LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Souderton, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, ETL, dbt, Tableau, Airflow, Apache Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a627bc801113951</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Security Software Engineer</t>
+          <t>Platform Engineer-US</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Certinia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,567 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>White Plains, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15fa432a086d4c1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bloomfield, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac78439c3d5984bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a693f67199d64d3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Morris Plains, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab713a681fd0429b</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8b99b8ea0db2061</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5dc36c16524b514</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Bloomington, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=281daf9216f9080a</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1ef5d5975efb63b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bloomfield, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36c0fd77f8d43c48</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Ledger Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>IntegriChain</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28193f1af5326eaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Engineer and Developer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, PostgreSQL, ETL, dbt, Tableau, Airflow, Apache Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a627bc801113951</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RDS, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d16f847f21e90057</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sevita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D28" t="n">
         <v>10.4</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62fecc0c2154e4b1</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50a46ce04515ea02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Security Software Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>University of Texas Health Science Center at San Antonio</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03327cd0d2ff3bea</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-18.xlsx
+++ b/results/job_matches_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - Active TS/SCI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LifeMD</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba2ab0e8ae4be68</t>
+          <t>https://www.indeed.com/viewjob?jk=f872fe833e94e41d</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Huntington Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,94 +566,94 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f2e0fa3bcda75e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba2ab0e8ae4be68</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Observability Engineer (Prometheus / Grafana / Datadog)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LifeMD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Huntington Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb8735550d94e63</t>
+          <t>https://www.indeed.com/viewjob?jk=3f2e0fa3bcda75e7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Observability Engineer (Prometheus / Grafana / Datadog)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vanda Pharmaceuticals</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f51f479af9282287</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb8735550d94e63</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Architect</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Vanda Pharmaceuticals</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,77 +661,77 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b7f11613741a49</t>
+          <t>https://www.indeed.com/viewjob?jk=f51f479af9282287</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b7f11613741a49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Pax8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb9ce5f60166ab4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alphanumeric Systems Inc</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafc1066893dd26c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
+          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Front-end Programmer Developer - II or Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=63a798e98d1f6f78</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RX USA LLC</t>
+          <t>Bamboo Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Souderton, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ea03efdc31e4c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Platform Engineer-US</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Certinia</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Engineer, IT Software</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fa432a086d4c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Front-end Programmer Developer - II or Senior</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac78439c3d5984bd</t>
+          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>RX USA LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Souderton, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a693f67199d64d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Platform Engineer-US</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Certinia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab713a681fd0429b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Industrial Scientific</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b99b8ea0db2061</t>
+          <t>https://www.indeed.com/viewjob?jk=23d358fe71511f6f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5dc36c16524b514</t>
+          <t>https://www.indeed.com/viewjob?jk=15fa432a086d4c1f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281daf9216f9080a</t>
+          <t>https://www.indeed.com/viewjob?jk=69eacc98e74b3522</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ef5d5975efb63b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac78439c3d5984bd</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36c0fd77f8d43c48</t>
+          <t>https://www.indeed.com/viewjob?jk=a693f67199d64d3d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Ledger Operations Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=ab713a681fd0429b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IntegriChain</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28193f1af5326eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b99b8ea0db2061</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer and Developer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, ETL, dbt, Tableau, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a627bc801113951</t>
+          <t>https://www.indeed.com/viewjob?jk=f5dc36c16524b514</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d16f847f21e90057</t>
+          <t>https://www.indeed.com/viewjob?jk=281daf9216f9080a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a46ce04515ea02</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ef5d5975efb63b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Security Software Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,40 +1441,285 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
+          <t>https://www.indeed.com/viewjob?jk=36c0fd77f8d43c48</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Senior Ledger Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>IntegriChain</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28193f1af5326eaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Engineer and Developer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, PostgreSQL, ETL, dbt, Tableau, Airflow, Apache Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a627bc801113951</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sr AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GE Aerospace</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d002c6cfe2bf32d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RDS, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d16f847f21e90057</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sevita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50a46ce04515ea02</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Security Software Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>San Antonio, TX, US USA</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D37" t="n">
         <v>10.4</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=03327cd0d2ff3bea</t>
         </is>

--- a/results/job_matches_2026-05-18.xlsx
+++ b/results/job_matches_2026-05-18.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data and Insight Analyst</t>
+          <t>Senior IT Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb46af131203645d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b886774f2191937</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Active TS/SCI</t>
+          <t>Data and Insight Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Dataflow, Scala, Kafka</t>
+          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f872fe833e94e41d</t>
+          <t>https://www.indeed.com/viewjob?jk=bb46af131203645d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - Active TS/SCI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LifeMD</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,104 +556,104 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba2ab0e8ae4be68</t>
+          <t>https://www.indeed.com/viewjob?jk=f872fe833e94e41d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Observability Engineer (Prometheus / Grafana / Datadog)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LifeMD</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Huntington Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f2e0fa3bcda75e7</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb8735550d94e63</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Observability Engineer (Prometheus / Grafana / Datadog)</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Vanda Pharmaceuticals</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb8735550d94e63</t>
+          <t>https://www.indeed.com/viewjob?jk=f51f479af9282287</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Senior Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vanda Pharmaceuticals</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,77 +661,77 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f51f479af9282287</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b7f11613741a49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Architect</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Pax8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b7f11613741a49</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb9ce5f60166ab4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pax8</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb9ce5f60166ab4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
         </is>
       </c>
     </row>
@@ -788,20 +788,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
+          <t>https://www.indeed.com/viewjob?jk=63a798e98d1f6f78</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bamboo Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a798e98d1f6f78</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ea03efdc31e4c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bamboo Health</t>
+          <t>Pacific Consulting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ea03efdc31e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=afb97449b7ed7b0d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Desmata Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
+          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -946,29 +946,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Front-end Programmer Developer - II or Senior</t>
+          <t>Engineer, IT Software</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Front-end Programmer Developer - II or Senior</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RX USA LLC</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Souderton, PA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
+          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Platform Engineer-US</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Certinia</t>
+          <t>RX USA LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Souderton, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Platform Engineer-US</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Industrial Scientific</t>
+          <t>Certinia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d358fe71511f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69eacc98e74b3522</t>
+          <t>https://www.indeed.com/viewjob?jk=ac78439c3d5984bd</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac78439c3d5984bd</t>
+          <t>https://www.indeed.com/viewjob?jk=a693f67199d64d3d</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a693f67199d64d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab713a681fd0429b</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab713a681fd0429b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b99b8ea0db2061</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b99b8ea0db2061</t>
+          <t>https://www.indeed.com/viewjob?jk=f5dc36c16524b514</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5dc36c16524b514</t>
+          <t>https://www.indeed.com/viewjob?jk=281daf9216f9080a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281daf9216f9080a</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ef5d5975efb63b</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ef5d5975efb63b</t>
+          <t>https://www.indeed.com/viewjob?jk=36c0fd77f8d43c48</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Senior Ledger Operations Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36c0fd77f8d43c48</t>
+          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Ledger Operations Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
+          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=69eacc98e74b3522</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Security Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d002c6cfe2bf32d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Sr AI Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d16f847f21e90057</t>
+          <t>https://www.indeed.com/viewjob?jk=d002c6cfe2bf32d3</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Security Software Engineer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
+          <t>https://www.indeed.com/viewjob?jk=03327cd0d2ff3bea</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>Fiduciary Tech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03327cd0d2ff3bea</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdadb345032fb3b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-18.xlsx
+++ b/results/job_matches_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,35 +573,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Observability Engineer (Prometheus / Grafana / Datadog)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>VantageScore</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb8735550d94e63</t>
+          <t>https://www.indeed.com/viewjob?jk=12497ac075998e0b</t>
         </is>
       </c>
     </row>
@@ -783,25 +783,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Pharma Applications Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a798e98d1f6f78</t>
+          <t>https://www.indeed.com/viewjob?jk=f82dba2e1c1cad0d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bamboo Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ea03efdc31e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=63a798e98d1f6f78</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data and AI Quality Automation Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pacific Consulting</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb97449b7ed7b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=471e912481eed840</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Desmata Inc</t>
+          <t>Bamboo Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ea03efdc31e4c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Pacific Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
+          <t>https://www.indeed.com/viewjob?jk=afb97449b7ed7b0d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>BIBA Practice - Big Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35842ddaad367b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Front-end Programmer Developer - II or Senior</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>Desmata Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RX USA LLC</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Souderton, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Platform Engineer-US</t>
+          <t>Engineer, IT Software</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Certinia</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
+          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Front-end Programmer Developer - II or Senior</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
+          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fa432a086d4c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>RX USA LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>Souderton, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac78439c3d5984bd</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Platform Engineer-US</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Certinia</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a693f67199d64d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab713a681fd0429b</t>
+          <t>https://www.indeed.com/viewjob?jk=d474f9c4c5e446c7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b99b8ea0db2061</t>
+          <t>https://www.indeed.com/viewjob?jk=15fa432a086d4c1f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5dc36c16524b514</t>
+          <t>https://www.indeed.com/viewjob?jk=69eacc98e74b3522</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281daf9216f9080a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac78439c3d5984bd</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ef5d5975efb63b</t>
+          <t>https://www.indeed.com/viewjob?jk=a693f67199d64d3d</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36c0fd77f8d43c48</t>
+          <t>https://www.indeed.com/viewjob?jk=ab713a681fd0429b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Ledger Operations Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b99b8ea0db2061</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Step Functions, S3, IAM, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69eacc98e74b3522</t>
+          <t>https://www.indeed.com/viewjob?jk=f5dc36c16524b514</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IntegriChain</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28193f1af5326eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=281daf9216f9080a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer and Developer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, ETL, dbt, Tableau, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a627bc801113951</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ef5d5975efb63b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Security Software Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
+          <t>https://www.indeed.com/viewjob?jk=36c0fd77f8d43c48</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Senior Ledger Operations Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d002c6cfe2bf32d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>Harbinger Motors Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a46ce04515ea02</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>IntegriChain</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03327cd0d2ff3bea</t>
+          <t>https://www.indeed.com/viewjob?jk=28193f1af5326eaa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer and Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fiduciary Tech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, DynamoDB, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, PostgreSQL, ETL, dbt, Tableau, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,217 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdadb345032fb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a627bc801113951</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>API Architect (Onsite Hybrid)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=463679cc517d5924</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ServiceTitan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab39fae8644125cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Security Software Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sr AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>GE Aerospace</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, RDS, Data Modeling, Git</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d002c6cfe2bf32d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sevita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50a46ce04515ea02</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>University of Texas Health Science Center at San Antonio</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03327cd0d2ff3bea</t>
         </is>
       </c>
     </row>
